--- a/research/traditional_assets/database/data/vietnam/vietnam_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_investments_asset_management.xlsx
@@ -588,40 +588,40 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.175609756097561</v>
+        <v>0.2463291139240506</v>
       </c>
       <c r="H2">
-        <v>0.175609756097561</v>
+        <v>0.2463291139240506</v>
       </c>
       <c r="I2">
-        <v>0.2092682926829268</v>
+        <v>0.1817721518987342</v>
       </c>
       <c r="J2">
-        <v>0.1663132220795892</v>
+        <v>0.1443378869532523</v>
       </c>
       <c r="K2">
-        <v>4.53</v>
+        <v>7.96</v>
       </c>
       <c r="L2">
-        <v>0.2209756097560976</v>
+        <v>0.2015189873417721</v>
       </c>
       <c r="M2">
-        <v>0.702</v>
+        <v>0.001</v>
       </c>
       <c r="N2">
-        <v>0.004365671641791045</v>
+        <v>1.7825311942959e-05</v>
       </c>
       <c r="O2">
-        <v>0.1549668874172185</v>
+        <v>0.0001256281407035176</v>
       </c>
       <c r="P2">
-        <v>0.702</v>
+        <v>0.001</v>
       </c>
       <c r="Q2">
-        <v>0.004365671641791045</v>
+        <v>1.7825311942959e-05</v>
       </c>
       <c r="R2">
-        <v>0.1549668874172185</v>
+        <v>0.0001256281407035176</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,73 +630,58 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>9.19</v>
+        <v>5.96</v>
       </c>
       <c r="V2">
-        <v>0.05715174129353233</v>
-      </c>
-      <c r="W2">
-        <v>0.3040268456375839</v>
+        <v>0.1062388591800356</v>
       </c>
       <c r="X2">
-        <v>0.07456518112877072</v>
-      </c>
-      <c r="Y2">
-        <v>0.2294616645088132</v>
-      </c>
-      <c r="Z2">
-        <v>0.8361545050373209</v>
-      </c>
-      <c r="AA2">
-        <v>0.139063549889121</v>
+        <v>0.114173136690931</v>
       </c>
       <c r="AB2">
-        <v>0.07166648421790059</v>
-      </c>
-      <c r="AC2">
-        <v>0.06739706567122036</v>
+        <v>0.106864245696427</v>
       </c>
       <c r="AD2">
-        <v>18.8</v>
+        <v>13.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>18.8</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>9.610000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="AH2">
-        <v>0.1046770601336303</v>
+        <v>0.1939655172413793</v>
       </c>
       <c r="AI2">
-        <v>0.3601532567049808</v>
+        <v>0.1421052631578947</v>
       </c>
       <c r="AJ2">
-        <v>0.05639340414294935</v>
+        <v>0.1184789440603394</v>
       </c>
       <c r="AK2">
-        <v>0.2234364101371774</v>
+        <v>0.08468104222821203</v>
       </c>
       <c r="AL2">
-        <v>0.08</v>
+        <v>0.694</v>
       </c>
       <c r="AM2">
-        <v>-0.665</v>
+        <v>-2.016</v>
       </c>
       <c r="AN2">
-        <v>4.224719101123595</v>
+        <v>1.831750339213026</v>
       </c>
       <c r="AO2">
-        <v>53.625</v>
+        <v>10.34582132564842</v>
       </c>
       <c r="AP2">
-        <v>2.159550561797753</v>
+        <v>1.023066485753053</v>
       </c>
       <c r="AQ2">
-        <v>-6.451127819548872</v>
+        <v>-3.561507936507936</v>
       </c>
     </row>
     <row r="3">
@@ -716,40 +701,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.175609756097561</v>
+        <v>0.2463291139240506</v>
       </c>
       <c r="H3">
-        <v>0.175609756097561</v>
+        <v>0.2463291139240506</v>
       </c>
       <c r="I3">
-        <v>0.2092682926829268</v>
+        <v>0.1817721518987342</v>
       </c>
       <c r="J3">
-        <v>0.1663132220795892</v>
+        <v>0.1443378869532523</v>
       </c>
       <c r="K3">
-        <v>4.53</v>
+        <v>7.96</v>
       </c>
       <c r="L3">
-        <v>0.2209756097560976</v>
+        <v>0.2015189873417721</v>
       </c>
       <c r="M3">
-        <v>0.702</v>
+        <v>0.001</v>
       </c>
       <c r="N3">
-        <v>0.004365671641791045</v>
+        <v>1.7825311942959e-05</v>
       </c>
       <c r="O3">
-        <v>0.1549668874172185</v>
+        <v>0.0001256281407035176</v>
       </c>
       <c r="P3">
-        <v>0.702</v>
+        <v>0.001</v>
       </c>
       <c r="Q3">
-        <v>0.004365671641791045</v>
+        <v>1.7825311942959e-05</v>
       </c>
       <c r="R3">
-        <v>0.1549668874172185</v>
+        <v>0.0001256281407035176</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -758,73 +743,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>9.19</v>
+        <v>5.96</v>
       </c>
       <c r="V3">
-        <v>0.05715174129353233</v>
-      </c>
-      <c r="W3">
-        <v>0.3040268456375839</v>
+        <v>0.1062388591800356</v>
       </c>
       <c r="X3">
-        <v>0.07456518112877072</v>
-      </c>
-      <c r="Y3">
-        <v>0.2294616645088132</v>
-      </c>
-      <c r="Z3">
-        <v>0.8361545050373209</v>
-      </c>
-      <c r="AA3">
-        <v>0.139063549889121</v>
+        <v>0.114173136690931</v>
       </c>
       <c r="AB3">
-        <v>0.07166648421790059</v>
-      </c>
-      <c r="AC3">
-        <v>0.06739706567122036</v>
+        <v>0.106864245696427</v>
       </c>
       <c r="AD3">
-        <v>18.8</v>
+        <v>13.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>18.8</v>
+        <v>13.5</v>
       </c>
       <c r="AG3">
-        <v>9.610000000000001</v>
+        <v>7.54</v>
       </c>
       <c r="AH3">
-        <v>0.1046770601336303</v>
+        <v>0.1939655172413793</v>
       </c>
       <c r="AI3">
-        <v>0.3601532567049808</v>
+        <v>0.1421052631578947</v>
       </c>
       <c r="AJ3">
-        <v>0.05639340414294935</v>
+        <v>0.1184789440603394</v>
       </c>
       <c r="AK3">
-        <v>0.2234364101371774</v>
+        <v>0.08468104222821203</v>
       </c>
       <c r="AL3">
-        <v>0.08</v>
+        <v>0.694</v>
       </c>
       <c r="AM3">
-        <v>-0.665</v>
+        <v>-2.016</v>
       </c>
       <c r="AN3">
-        <v>4.224719101123595</v>
+        <v>1.831750339213026</v>
       </c>
       <c r="AO3">
-        <v>53.625</v>
+        <v>10.34582132564842</v>
       </c>
       <c r="AP3">
-        <v>2.159550561797753</v>
+        <v>1.023066485753053</v>
       </c>
       <c r="AQ3">
-        <v>-6.451127819548872</v>
+        <v>-3.561507936507936</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_investments_asset_management.xlsx
@@ -587,101 +587,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G2">
-        <v>0.2463291139240506</v>
-      </c>
-      <c r="H2">
-        <v>0.2463291139240506</v>
-      </c>
-      <c r="I2">
-        <v>0.1817721518987342</v>
-      </c>
-      <c r="J2">
-        <v>0.1443378869532523</v>
-      </c>
       <c r="K2">
-        <v>7.96</v>
-      </c>
-      <c r="L2">
-        <v>0.2015189873417721</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1.7825311942959e-05</v>
-      </c>
-      <c r="O2">
-        <v>0.0001256281407035176</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.7825311942959e-05</v>
-      </c>
-      <c r="R2">
-        <v>0.0001256281407035176</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>5.96</v>
+        <v>10</v>
       </c>
       <c r="V2">
-        <v>0.1062388591800356</v>
+        <v>0.390625</v>
+      </c>
+      <c r="W2">
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0.114173136690931</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="Y2">
+        <v>-0.08479692846796255</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.106864245696427</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="AC2">
+        <v>-0.08479692846796255</v>
       </c>
       <c r="AD2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>7.54</v>
+        <v>-10</v>
       </c>
       <c r="AH2">
-        <v>0.1939655172413793</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.1421052631578947</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.1184789440603394</v>
+        <v>-0.641025641025641</v>
       </c>
       <c r="AK2">
-        <v>0.08468104222821203</v>
+        <v>-0.3174603174603174</v>
       </c>
       <c r="AL2">
-        <v>0.694</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-2.016</v>
-      </c>
-      <c r="AN2">
-        <v>1.831750339213026</v>
-      </c>
-      <c r="AO2">
-        <v>10.34582132564842</v>
-      </c>
-      <c r="AP2">
-        <v>1.023066485753053</v>
-      </c>
-      <c r="AQ2">
-        <v>-3.561507936507936</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +671,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IDJ Vietnam Investment Joint Stock Company (HNX:IDJ)</t>
+          <t>Tri Viet Securities Joint Stock Corporation (HOSE:TVB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -700,101 +679,80 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G3">
-        <v>0.2463291139240506</v>
-      </c>
-      <c r="H3">
-        <v>0.2463291139240506</v>
-      </c>
-      <c r="I3">
-        <v>0.1817721518987342</v>
-      </c>
-      <c r="J3">
-        <v>0.1443378869532523</v>
-      </c>
       <c r="K3">
-        <v>7.96</v>
-      </c>
-      <c r="L3">
-        <v>0.2015189873417721</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>1.7825311942959e-05</v>
-      </c>
-      <c r="O3">
-        <v>0.0001256281407035176</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.001</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>1.7825311942959e-05</v>
-      </c>
-      <c r="R3">
-        <v>0.0001256281407035176</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>5.96</v>
+        <v>10</v>
       </c>
       <c r="V3">
-        <v>0.1062388591800356</v>
+        <v>0.390625</v>
+      </c>
+      <c r="W3">
+        <v>0</v>
       </c>
       <c r="X3">
-        <v>0.114173136690931</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="Y3">
+        <v>-0.08479692846796255</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.106864245696427</v>
+        <v>0.08479692846796255</v>
+      </c>
+      <c r="AC3">
+        <v>-0.08479692846796255</v>
       </c>
       <c r="AD3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>7.54</v>
+        <v>-10</v>
       </c>
       <c r="AH3">
-        <v>0.1939655172413793</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.1421052631578947</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.1184789440603394</v>
+        <v>-0.641025641025641</v>
       </c>
       <c r="AK3">
-        <v>0.08468104222821203</v>
+        <v>-0.3174603174603174</v>
       </c>
       <c r="AL3">
-        <v>0.694</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-2.016</v>
-      </c>
-      <c r="AN3">
-        <v>1.831750339213026</v>
-      </c>
-      <c r="AO3">
-        <v>10.34582132564842</v>
-      </c>
-      <c r="AP3">
-        <v>1.023066485753053</v>
-      </c>
-      <c r="AQ3">
-        <v>-3.561507936507936</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
